--- a/InputData/dist-heat/EoCtUH/Efficiency of Conversion to Usable Heat.xlsx
+++ b/InputData/dist-heat/EoCtUH/Efficiency of Conversion to Usable Heat.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Modeling\EPS\US\eps-us\InputData\dist-heat\EoCtUH\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\dist-heat\EoCtUH\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A213CE0-B304-426A-B2B8-495056E14A1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78DC9C74-CE95-4180-A028-32C7D110C6F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="60840" yWindow="2385" windowWidth="24900" windowHeight="14490" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11235" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -25,6 +25,9 @@
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -32,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="55">
   <si>
     <t>Source:</t>
   </si>
@@ -197,12 +200,6 @@
   </si>
   <si>
     <t>Heat pumps are represented by using an efficiency greater than 1</t>
-  </si>
-  <si>
-    <t>green hydrogen</t>
-  </si>
-  <si>
-    <t>low carbon hydrogen</t>
   </si>
 </sst>
 </file>
@@ -614,17 +611,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B31"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="47.453125" customWidth="1"/>
+    <col min="2" max="2" width="47.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -632,122 +629,122 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" s="2">
         <v>2014</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B10" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B12" s="2">
         <v>2018</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B14" s="6" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>31</v>
       </c>
@@ -764,17 +761,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G32"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="46.453125" customWidth="1"/>
+    <col min="1" max="1" width="46.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>2000</v>
       </c>
@@ -797,7 +794,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>0.65</v>
       </c>
@@ -820,25 +817,25 @@
         <v>0.73</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="8">
         <f>AVERAGE(A3:G3)</f>
         <v>0.7014285714285714</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>37</v>
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>38</v>
       </c>
@@ -849,7 +846,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>1</v>
       </c>
@@ -860,7 +857,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2</v>
       </c>
@@ -871,7 +868,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>3</v>
       </c>
@@ -882,7 +879,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>4</v>
       </c>
@@ -893,7 +890,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>5</v>
       </c>
@@ -904,7 +901,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>6</v>
       </c>
@@ -915,7 +912,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>7</v>
       </c>
@@ -926,7 +923,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>8</v>
       </c>
@@ -937,7 +934,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>9</v>
       </c>
@@ -948,7 +945,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>10</v>
       </c>
@@ -959,7 +956,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>11</v>
       </c>
@@ -970,7 +967,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>12</v>
       </c>
@@ -981,7 +978,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>13</v>
       </c>
@@ -992,7 +989,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>14</v>
       </c>
@@ -1003,7 +1000,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>15</v>
       </c>
@@ -1014,7 +1011,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>16</v>
       </c>
@@ -1025,7 +1022,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>50</v>
       </c>
@@ -1034,17 +1031,17 @@
         <v>3.6642857142857141</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>53</v>
       </c>
@@ -1063,19 +1060,19 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.453125" customWidth="1"/>
-    <col min="2" max="2" width="15.1796875" customWidth="1"/>
+    <col min="1" max="1" width="25.42578125" customWidth="1"/>
+    <col min="2" max="2" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>20</v>
       </c>
@@ -1084,7 +1081,7 @@
         <v>2.5702346938775507</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -1093,7 +1090,7 @@
         <v>0.7014285714285714</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -1102,7 +1099,7 @@
         <v>0.7014285714285714</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -1111,7 +1108,7 @@
         <v>0.7014285714285714</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -1120,7 +1117,7 @@
         <v>0.7014285714285714</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -1129,7 +1126,7 @@
         <v>0.7014285714285714</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -1138,7 +1135,7 @@
         <v>0.7014285714285714</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -1147,7 +1144,7 @@
         <v>0.7014285714285714</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>28</v>
       </c>
@@ -1156,29 +1153,11 @@
         <v>0.7014285714285714</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>29</v>
       </c>
       <c r="B11" s="4">
-        <f>Data!A$6</f>
-        <v>0.7014285714285714</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>55</v>
-      </c>
-      <c r="B12" s="4">
-        <f>Data!A$6</f>
-        <v>0.7014285714285714</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>56</v>
-      </c>
-      <c r="B13" s="4">
         <f>Data!A$6</f>
         <v>0.7014285714285714</v>
       </c>
